--- a/contract.xlsx
+++ b/contract.xlsx
@@ -16,10 +16,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="70">
   <si>
-    <t>Hisob-varaq shartnoma 3</t>
-  </si>
-  <si>
-    <t>12/04/2025 yil                                                                                                                Chelak shaxri</t>
+    <t>Hisob-varaq shartnoma undefined</t>
+  </si>
+  <si>
+    <t>08/11/2025 yil                                                                                                                Chelak shaxri</t>
   </si>
   <si>
     <r>

--- a/contract.xlsx
+++ b/contract.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="70">
   <si>
-    <t>Hisob-varaq shartnoma undefined</t>
+    <t>Hisob-varaq shartnoma 27</t>
   </si>
   <si>
     <t>08/11/2025 yil                                                                                                                Chelak shaxri</t>
